--- a/gtm-product/GTM_定價模型.xlsx
+++ b/gtm-product/GTM_定價模型.xlsx
@@ -488,7 +488,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gate-to-Market 定價模型｜假設輸入</t>
+          <t>Landfall 登岸 定價模型｜假設輸入</t>
         </is>
       </c>
     </row>
